--- a/data/exports/houston_energy_mapper_v1.xlsx
+++ b/data/exports/houston_energy_mapper_v1.xlsx
@@ -619,7 +619,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Company website not publicly accessible</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Company website not publicly accessible</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -729,7 +729,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Company website not publicly accessible</t>
+          <t>Founders not listed on company website. The page mentions a team exists and that ZEG is a spinout from IFE, but no individual names or roles are provided in the webpage content.</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -782,7 +782,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Company website not publicly accessible</t>
+          <t>Dr. Michal Okoniewski (Chief Scientific Officer &amp; Co-Founder) - Co-founded Acceleware in 2004; PhD in Electrical Engineering from Technical University, Gdansk; Fellow of IEEE; Professor at University of Calgary Schulich School of Engineering</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -888,7 +888,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Company website not publicly accessible</t>
+          <t>Founders not listed on company website. The page describes Prof. Selva's research group at the University of Houston but does not list any founders or C-suite executives for AmpsUP. No BE Fellows match provided.</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -941,7 +941,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Founders not listed on company website. The page mentions 'Meet the Team' but no individual names or roles are provided in the extracted content.</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1202,7 +1202,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Company website not publicly accessible</t>
+          <t>Becca Segel (CEO and Founder) - Chemical engineering PhD student at University of Pittsburgh; 8 years of research experience in flow battery field; Forbes 30u30 in Industry &amp; Manufacturing</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Company website not publicly accessible</t>
+          <t>Founders not listed on company website.</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -1626,7 +1626,7 @@
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Company website not publicly accessible</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -2266,7 +2266,7 @@
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Shiv Bhakta (CEO &amp; Co-Founder) - MIT Sloan MBA, MIT MS, University of Houston BS; experience at Department of Energy, ExxonMobil, Verizon, MUUS Climate Partners; Forbes 30 Under 30; Richard Swartwout (CTO &amp; Co-Founder) - MIT PhD in Solar R&amp;D and Printed Electronics; Tata Center Fellow; co-developed MIT's GridEdge program; holds 3 patents in Active Surfaces IP portfolio</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Founders not listed on company website. The page only contains information about investors, partners, and a careers section, with no founder or leadership team details.</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -3036,7 +3036,7 @@
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Company website not publicly accessible</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
@@ -3248,7 +3248,7 @@
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Founders not listed on company website. The page describes Electric Hydrogen's project development services and team capabilities in general terms, but no individual names or leadership roles are mentioned.</t>
+          <t>Founders not listed on company website. The page describes Electric Hydrogen's project development capabilities and partnerships but does not name any founders or leadership team members.</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
@@ -3900,7 +3900,7 @@
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>Founders not listed on company website. Company explicitly states it is operating in stealth mode and has chosen not to publish management profiles. General background signals mentioned (PhDs in science/engineering, prior IPO experience, backgrounds in science/technology/finance) but no individual names or roles are disclosed.</t>
+          <t>Founders not listed on company website. Company explicitly states it is operating in stealth mode and has chosen not to publish management profiles. General background signals mentioned collectively: founding scientists with PhDs in science or engineering, backgrounds in nuclear fusion research, prior experience founding or scaling technology companies to IPOs exceeding $1 billion market cap.</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
@@ -4169,7 +4169,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>Founders not listed on company website. The page mentions Hans-Werner Kaas as a new leadership addition (not a founder), but no founder names or C-suite titles are surfaced in the provided webpage content.</t>
+          <t>Founders not listed on company website. Only a leadership addition (Hans-Werner Kaas) is mentioned in a news headline, but no founders or C-suite roles are explicitly listed on the page.</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -4862,7 +4862,7 @@
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Alisha Fredriksson (Co-Founder &amp; CEO) - Previously helped build Liquid Wind (maritime electro-fuel startup); managed global partnerships at Generation (non-profit founded by McKinsey &amp; Company); Founding Class at Minerva University; studied at Mahindra United World College of India; Roujia Wen (Co-Founder &amp; Advisor)</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Howard Yuh (CEO &amp; Co-founder) - PhD Nuclear Engineering (Applied Plasma Physics), MIT; USDOE Oppenheimer Science and Energy Leadership Program inaugural cohort; Ethan Schartman (CTO &amp; Co-founder) - PhD Plasma Physics, Princeton; 16 years hardware deep tech innovation; Kevin Tritz (COO &amp; Co-founder) - PhD Engineering Physics, University of Wisconsin Madison; 22 years systems engineering and integration expertise; Duncan O'Brien Jr. (CFO and Chief Strategy Officer) - MBA, Stanford; ex-Goldman Sachs, General Electric, Cox Enterprises; 40 years experience in strategy and corporate finance</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
@@ -5551,7 +5551,7 @@
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>Founders not listed on company website. Only a Business Development Manager (Simon Espinosa) is mentioned on the page.</t>
+          <t>Founders not listed on company website. Only a Business Development Manager (Simon Espinosa) is mentioned on the page, with no founders or C-suite leadership listed.</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>Founders not listed on company website. The page contains general company information, mission, and values but no individual team members, founders, or leadership names are surfaced in the provided content.</t>
+          <t>Founders not listed on company website. The page references a Leadership Team &amp; Board section but no individual names or roles are surfaced in the provided webpage content.</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Company website not publicly accessible</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K141" s="5" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Hasan Kazmi (Co-founder &amp; Chief Business Officer) - MSTC, BComm. (Law), Finance &amp; Strategy; Rafat Jami (Co-Founder &amp; Chief Executive Officer) - PhD*, P.Eng., Aerospace Engineer; David Serrano (Chief Technology Officer) - M.Sc., MSS, P.Eng., Aerospace Engineer</t>
         </is>
       </c>
       <c r="L141" s="5" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="K142" s="5" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Mohammed Njie (CEO)</t>
         </is>
       </c>
       <c r="L142" s="5" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="K152" s="5" t="inlineStr">
         <is>
-          <t>Founders not listed on company website. The page mentions 'Dr. Jennifer Lalli' in a news headline and 'Maggie Bump' with an Emerita status, but neither is identified as a founder or C-suite executive in the webpage content.</t>
+          <t>Founders not listed on company website. The page mentions Dr. Jennifer Lalli and Maggie Bump in news headlines, but their roles/titles are not explicitly stated on this page. No founder or C-suite leadership section is present.</t>
         </is>
       </c>
       <c r="L152" s="5" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="K158" s="5" t="inlineStr">
         <is>
-          <t>Founders not listed on company website. The page describes the company's technology and products but does not name any founders or leadership team members.</t>
+          <t>Founders not listed on company website. The page describes the company's technology and products but does not mention any founders or leadership team members.</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="K159" s="5" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Connor Crawford (Chief Executive Officer, Cofounder) - Spun out of UT Austin's Texas Robotics Labs; Zach Jurecek (Chief Technology Officer, Cofounder) - Spun out of UT Austin's Texas Robotics Labs</t>
         </is>
       </c>
       <c r="L159" s="5" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="K178" s="5" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Tim Fairley-Wax (CEO) - Developed Aquora's technology at University of Michigan; Chain Reaction Innovations Startup Fellow at Argonne National Laboratory.; Steve Skerlos (COO) - PhD; UM distinguished faculty fellow in sustainability; seasoned entrepreneur with multiple commercialized technologies from University of Michigan.</t>
         </is>
       </c>
       <c r="L178" s="5" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="K183" s="5" t="inlineStr">
         <is>
-          <t>Founders not listed on company website.</t>
+          <t>Tobias Kraft (Founder, CEO) - Co-founded Teren; career focused on analyzing environmental data for real-world problems</t>
         </is>
       </c>
       <c r="L183" s="5" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="K200" s="5" t="inlineStr">
         <is>
-          <t>Founders not listed on company website.</t>
+          <t>Founders not listed on company website. The page focuses on product features, press coverage, and funding announcements with no team or leadership section visible.</t>
         </is>
       </c>
       <c r="L200" s="5" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="K217" s="5" t="inlineStr">
         <is>
-          <t>Founders not listed on company website. The page includes a company origin story mentioning the company started in 2021 but does not name any specific founders or leadership team members.</t>
+          <t>Founders not listed on company website. The page includes a brief company origin story mentioning the company started in 2021 but does not name any founders or leadership team members.</t>
         </is>
       </c>
       <c r="L217" s="5" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="K223" s="5" t="inlineStr">
         <is>
-          <t>No website available</t>
+          <t>Company website not publicly accessible</t>
         </is>
       </c>
       <c r="L223" s="5" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="K229" s="5" t="inlineStr">
         <is>
-          <t>Founders not listed on company website. The page mentions MMT was founded in 2014 but does not name any founders or leadership team members.</t>
+          <t>Company website not publicly accessible</t>
         </is>
       </c>
       <c r="L229" s="5" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="K245" s="5" t="inlineStr">
         <is>
-          <t>No founders or C-suite executives listed on the page. Only a Research Scientist (Dr. Sanjana Senthilkumar) and a Production Technician (Zoe Hopkinson) are mentioned, neither of whom are identified as founders or executive leadership.</t>
+          <t>No founders or C-suite executives listed on the page. Only a Research Scientist (Dr Sanjana Senthilkumar) and a Production Technician (Zoe Hopkinson) are mentioned, neither of whom are identified as founders or C-suite leadership.</t>
         </is>
       </c>
       <c r="L245" s="5" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="K254" s="5" t="inlineStr">
         <is>
-          <t>Founders not listed on company website. The page contains minimal content with no team member names or leadership information visible.</t>
+          <t>Founders not listed on company website. The page contains only general company information, contact details, and navigation links with no team member names or roles.</t>
         </is>
       </c>
       <c r="L254" s="5" t="inlineStr">
@@ -37886,7 +37886,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
@@ -50774,11 +50774,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -50827,7 +50827,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>VENTURE_SCALE (score ≥ 7.0)</t>
+          <t>VENTURE_SCALE (score &gt;= 7.0)</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -50839,7 +50839,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>BORDERLINE (score 4.0–6.9)</t>
+          <t>BORDERLINE (score 4.0-6.9)</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -50899,7 +50899,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>≥ 7.0 per classifier prompt v1.1</t>
+          <t>&gt;= 7.0 per classifier prompt v1.1</t>
         </is>
       </c>
     </row>
@@ -50911,7 +50911,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>FlowCellutions: '8.0 base − 1.0 Office Hours = 7.0 still clears VENTURE_SCALE'</t>
+          <t>FlowCellutions: '8.0 base - 1.0 Office Hours = 7.0 still clears VENTURE_SCALE'</t>
         </is>
       </c>
     </row>
@@ -50930,7 +50930,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Event presenter rosters 2021–2024 (4 years × ~45 presenters)</t>
+          <t>Event presenter rosters 2021-2024 (4 years x ~45 presenters)</t>
         </is>
       </c>
     </row>
@@ -50966,7 +50966,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>901 Texas energy filings 2019–2024</t>
+          <t>901 Texas energy filings 2019-2024</t>
         </is>
       </c>
     </row>
@@ -50997,7 +50997,7 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Goose Capital portfolio</t>
+          <t>GOOSE Capital portfolio</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -51009,7 +51009,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>EnergyCapital Ventures portfolio</t>
+          <t>Energy Capital Ventures portfolio</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -51155,244 +51155,324 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Flywheel / Human Validation State</t>
+          <t>Domain Resolution (added at QA)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Manual override records</t>
+          <t>Pre-coalesce VS+BORDERLINE missing canonical_domain</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>854</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Review round 1 (Step 12)</t>
+          <t>Resolved via cross-source coalesce</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>11 BORDERLINE → VENTURE_SCALE promotions</t>
+          <t>340</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Review round 2 (Step 13 flywheel)</t>
+          <t>Still missing (sources never captured URLs)</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>2 promotions + 4 score adjustments via re-classification</t>
+          <t>514</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>validated_examples.jsonl</t>
+          <t>Sources requiring Phase 2 harvester rebuild</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Active — auto-injected into classifier calls</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+          <t>DCVC, Lowercarbon Capital, Energy Capital Ventures, EnergyTech Nexus</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Phase 2 fix</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Move coalesce step into dedup pipeline; rebuild listed harvesters with two-step (listing -&gt; detail) structure to capture URLs at source</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Founder Pedigree Enrichment</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Total VS+BORDERLINE candidates</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>340</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>Records with website successfully scraped</t>
+          <t>Total VS+BORDERLINE candidates (all scrape passes)</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>340</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>Records with founder names extracted</t>
+          <t>Records with website successfully scraped</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>212 (initial) + 149 (re-scrape after coalesce)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Records with BE Fellows confirmed match</t>
+          <t>Records with founder names extracted (total)</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>149</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Records with website fetch failed</t>
+          <t xml:space="preserve">  Initial pass (212 fetched pages)</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>138</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Records with no website available</t>
+          <t xml:space="preserve">  Re-scrape pass (post-coalesce, 149 targeted)</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>10 additional</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>Path coverage</t>
+          <t>Records with BE Fellows confirmed match</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>14 paths per record: /about, /about-us, /team, /our-team, /leadership, /people, /our-people, /company, /our-story, /who-we-are, /founders, /management, /about/team, /about/leadership, plus homepage fallback</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>Failure mode breakdown</t>
+          <t>Records with no website available</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>JS-rendered SPAs (~40%), Cloudflare/WAF blocks (~35%), parked/defunct domains (~25%)</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>Phase 2 enrichment work flagged</t>
+          <t>Path coverage</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
+          <t>14 paths per record (/about, /about-us, /team, /our-team, /leadership, /people, /our-people, /company, /our-story, /who-we-are, /founders, /management, /about/team, /about/leadership) + homepage fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Failure modes</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>JS-rendered SPAs (~40%), Cloudflare/WAF blocks (~35%), parked/defunct domains (~25%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Phase 2 work flagged</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
           <t>Playwright-based JS rendering, cloudscraper or curl_cffi for WAF bypass, domain validation pass</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>Deduplication</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>Duplicates removed</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-    </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>Excluded records</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Flywheel / Human Validation State</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Manual override records</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>Known Gaps</t>
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Review round 1 (Step 12)</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>11 BORDERLINE -&gt; VENTURE_SCALE promotions</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>Holocene</t>
+          <t>Review round 2 (Step 13 flywheel)</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Not captured in any harvested source — Phase 2 priority</t>
+          <t>2 promotions + 4 score adjustments via re-classification</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
+          <t>validated_examples.jsonl</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Active — auto-injected into classifier calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>Deduplication</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Duplicates removed</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>Excluded records</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>Known Gaps</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Holocene</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Not captured in any harvested source — Phase 2 priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
           <t>CO2 Lock</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>LLM parse failure on team page (truncated background_signals); founders identified but not persisted</t>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>LLM parse failure on team page (truncated output); founders identified but not persisted</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A68:B68"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A58:B58"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A35:B35"/>
   </mergeCells>
